--- a/src/test/resources/OQ TestData/OQ SpecData.xlsx
+++ b/src/test/resources/OQ TestData/OQ SpecData.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2e249e2788c06855/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\MM_Project\Material_Management_Product\src\test\resources\OQ TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="8_{1AAB6724-2E34-47F2-96AF-849A1743D98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59F16465-16BC-4622-978B-D5CE9F5F1529}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7110263-424F-46E8-B59A-3A31D6D272D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{E9FB058C-3827-490C-9E48-CE8BBC79D4AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{E9FB058C-3827-490C-9E48-CE8BBC79D4AA}"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialSpecification" sheetId="1" r:id="rId1"/>
     <sheet name="ProductSpecification" sheetId="2" r:id="rId2"/>
     <sheet name="Checklist" sheetId="3" r:id="rId3"/>
+    <sheet name="Security Group(MR_MA)" sheetId="4" r:id="rId4"/>
+    <sheet name="User Creation(MR_MA)" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="121">
   <si>
     <t>Name Of The Test</t>
   </si>
@@ -292,13 +294,197 @@
   </si>
   <si>
     <t>Is De-dusting performed for received containers/bags?</t>
+  </si>
+  <si>
+    <t>Security Group Name</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Privileges</t>
+  </si>
+  <si>
+    <t>Master Reviewer</t>
+  </si>
+  <si>
+    <t>MasterApprover</t>
+  </si>
+  <si>
+    <t>MASTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUICK_PRODUCT,
+QUICK_PRODUCT_VIEW,
+QUICK_PRODUCT_REVIEW,
+PRODUCT,
+PRODUCT_REVIEW,
+PRODUCT_IN_ACTIVE_REVIEW,
+PRODUCT_VIEW,
+NDC,
+NDC_IN_ACTIVE_REVIEW,
+NDC_REVIEW,
+NDC_VIEW,
+PRODUCT_SPECIFICATION,
+PRODUCT_SPECIFICATION_VIEW,
+PRODUCT_SPECIFICATION_REVIEW,
+VENDOR_SUPPLIER,
+VENDOR_SUPPLIER_VIEW,
+VENDOR_SUPPLIER_REVIEW,
+VENDOR_MANUFACTURER,
+VENDOR_MANUFACTURER_VIEW,
+VENDOR_MANUFACTURER_REVIEW,
+VENDOR_DETAILS,
+VENDOR_DETAILS_LIST,
+MATERIAL_CATEGORY,
+MATERIAL_CATEGORY_REVIEW,
+MATERIAL_CATEGORY_VIEW,
+MATERIAL_DETAILS,
+MATERIAL_DETAILS_VIEW,
+MATERIAL_DETAILS_REVIEW,
+MATERIAL_SPECIFICATION,
+MATERIAL_SPECIFICATION_VIEW,
+MATERIAL_SPECIFICATION_REVIEW,
+EQUIPMENT,
+EQUIPMENT_VIEW,
+EQUIPMENT_REVIEW
+</t>
+  </si>
+  <si>
+    <t>DEPARTMENT,
+DEPARTMENT_VIEW,
+DEPARTMENT_APPROVE,
+SECURITY_GROUP,
+SECURITY_GROUP_VIEW,
+SECURITY_GROUP_APPROVE,
+FACILITY,
+FACILITY_APPROVE,
+FACILITY_VIEW,
+QUICK_PRODUCT,
+QUICK_PRODUCT_VIEW,
+QUICK_PRODUCT_APPROVE,
+PRODUCT,
+PRODUCT_APPROVE,
+PRODUCT_IN_ACTIVE_APPROVE,
+PRODUCT_VIEW,
+NDC,
+NDC_IN_ACTIVE_APPROVE,
+NDC_REVIEW,
+NDC_VIEW,
+PRODUCT_SPECIFICATION,
+PRODUCT_SPECIFICATION_VIEW,
+PRODUCT_SPECIFICATION_APPROVE,
+VENDOR_SUPPLIER,
+VENDOR_SUPPLIER_VIEW,
+VENDOR_SUPPLIER_APPROVE,
+VENDOR_MANUFACTURER,
+VENDOR_MANUFACTURER_VIEW,
+VENDOR_MANUFACTURER_APPROVE,
+VENDOR_DETAILS,
+VENDOR_DETAILS_LIST,
+MATERIAL_CATEGORY,
+MATERIAL_CATEGORY_APPROVE,
+MATERIAL_CATEGORY_VIEW,
+MATERIAL_DETAILS,
+MATERIAL_DETAILS_VIEW,
+MATERIAL_DETAILS_APPROVE,
+MATERIAL_SPECIFICATION,
+MATERIAL_SPECIFICATION_VIEW,
+MATERIAL_SPECIFICATION_APPROVE,
+EQUIPMENT,
+EQUIPMENT_VIEW,
+EQUIPMENT_APPROVE</t>
+  </si>
+  <si>
+    <t>Master Approver</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Mobile Number</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Temporary Password</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Designation</t>
+  </si>
+  <si>
+    <t>admin12</t>
+  </si>
+  <si>
+    <t>Reviewer</t>
+  </si>
+  <si>
+    <t>Master_Reviewer</t>
+  </si>
+  <si>
+    <t>advitha@gmail.com</t>
+  </si>
+  <si>
+    <t>Approver</t>
+  </si>
+  <si>
+    <t>Master_Approver</t>
+  </si>
+  <si>
+    <t>Date Of Joining</t>
+  </si>
+  <si>
+    <t>JD Approved On</t>
+  </si>
+  <si>
+    <t>Training Completed On</t>
+  </si>
+  <si>
+    <t>Job Code</t>
+  </si>
+  <si>
+    <t>Mode Of Training</t>
+  </si>
+  <si>
+    <t>Require Questionnaire</t>
+  </si>
+  <si>
+    <t>Code-1</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Self Training</t>
+  </si>
+  <si>
+    <t>Sai kumar</t>
+  </si>
+  <si>
+    <t>Ganesh</t>
+  </si>
+  <si>
+    <t>sai1</t>
+  </si>
+  <si>
+    <t>ganesh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,6 +495,38 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,10 +549,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -351,8 +570,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1423,4 +1653,236 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F686202B-84BC-4AB8-BABC-48E235FD80B2}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="6"/>
+    <col min="4" max="4" width="139.85546875" style="6" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="321.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08137D20-E1D9-4F66-BBB4-052A407E4649}">
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18" style="9" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" style="9" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="9"/>
+    <col min="6" max="6" width="19.7109375" style="9" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="12" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="9"/>
+    <col min="10" max="10" width="20.7109375" style="9" customWidth="1"/>
+    <col min="11" max="11" width="22.5703125" style="9" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="9" customWidth="1"/>
+    <col min="13" max="13" width="21.85546875" style="9" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" style="9" customWidth="1"/>
+    <col min="15" max="15" width="18.5703125" style="9" customWidth="1"/>
+    <col min="16" max="16" width="23.140625" style="9" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="9">
+        <v>1004</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" s="10">
+        <v>46004</v>
+      </c>
+      <c r="L2" s="10">
+        <v>46034</v>
+      </c>
+      <c r="M2" s="10">
+        <v>46068</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>1005</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K3" s="10">
+        <v>46004</v>
+      </c>
+      <c r="L3" s="10">
+        <v>46034</v>
+      </c>
+      <c r="M3" s="10">
+        <v>46068</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{5680BB8A-21A9-4211-A78A-2F65BD244A13}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/OQ TestData/OQ SpecData.xlsx
+++ b/src/test/resources/OQ TestData/OQ SpecData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800"/>
+    <workbookView windowWidth="19200" windowHeight="6800" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="MaterialSpecification" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="Checklist" sheetId="3" r:id="rId3"/>
     <sheet name="Security Group(MR_MA)" sheetId="4" r:id="rId4"/>
     <sheet name="User Creation(MR_MA)" sheetId="5" r:id="rId5"/>
+    <sheet name="User Creation(MMIni_MMRev_MMAp)" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="125">
   <si>
     <t>Name Of The Test</t>
   </si>
@@ -434,10 +435,10 @@
     <t>Require Questionnaire</t>
   </si>
   <si>
-    <t>Sai kumar</t>
-  </si>
-  <si>
-    <t>sai1</t>
+    <t>New Password</t>
+  </si>
+  <si>
+    <t>test2</t>
   </si>
   <si>
     <t>admin12</t>
@@ -449,28 +450,40 @@
     <t>Reviewer</t>
   </si>
   <si>
-    <t>Master_Reviewer</t>
-  </si>
-  <si>
-    <t>Code-1</t>
+    <t>Chemical Room are In-Charge</t>
   </si>
   <si>
     <t>Self Training</t>
   </si>
   <si>
-    <t>Ganesh</t>
-  </si>
-  <si>
-    <t>advitha@gmail.com</t>
-  </si>
-  <si>
-    <t>ganesh</t>
+    <t>Admin@12</t>
+  </si>
+  <si>
+    <t>test3</t>
   </si>
   <si>
     <t>Approver</t>
   </si>
   <si>
-    <t>Master_Approver</t>
+    <t>test4</t>
+  </si>
+  <si>
+    <t>test41</t>
+  </si>
+  <si>
+    <t>MM Initiator</t>
+  </si>
+  <si>
+    <t>test5</t>
+  </si>
+  <si>
+    <t>MM Reviewer</t>
+  </si>
+  <si>
+    <t>test6</t>
+  </si>
+  <si>
+    <t>MM Approver</t>
   </si>
 </sst>
 </file>
@@ -506,6 +519,14 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -519,14 +540,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1001,7 +1014,7 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1129,28 +1142,34 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1481,79 +1500,79 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="2" width="26" style="12"/>
-    <col min="3" max="3" width="31.8545454545455" style="12" customWidth="1"/>
-    <col min="4" max="16384" width="26" style="12"/>
+    <col min="1" max="2" width="26" style="18"/>
+    <col min="3" max="3" width="31.8545454545455" style="18" customWidth="1"/>
+    <col min="4" max="16384" width="26" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="87" spans="1:8">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="18">
         <v>47</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="18">
         <v>49</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="18" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1561,107 +1580,107 @@
       <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="18">
         <v>47</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="18">
         <v>49</v>
       </c>
       <c r="G5" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="18" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="18">
         <v>121</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="18">
         <v>123</v>
       </c>
       <c r="G6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="18">
         <v>285</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="18">
         <v>315</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" ht="29" spans="1:8">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" ht="29" spans="1:8">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" ht="29" spans="1:8">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="18" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1677,373 +1696,373 @@
   <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="14.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="3" width="26" style="11"/>
-    <col min="4" max="4" width="31.8545454545455" style="11" customWidth="1"/>
-    <col min="5" max="16384" width="26" style="11"/>
+    <col min="1" max="3" width="26" style="17"/>
+    <col min="4" max="4" width="31.8545454545455" style="17" customWidth="1"/>
+    <col min="5" max="16384" width="26" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="43.5" spans="1:8">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" ht="72.5" spans="1:8">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" ht="29" spans="1:8">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="17">
         <v>95</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="17">
         <v>100</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" ht="29" spans="1:8">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="17">
         <v>0.95</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="17">
         <v>2</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="17">
         <v>6</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="17">
         <v>8</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="17">
         <v>30</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="17">
         <v>50</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" ht="29" spans="1:8">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="17">
         <v>0</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="17">
         <v>0.1</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="17">
         <v>0</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="17">
         <v>0.1</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="17">
         <v>0</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="17">
         <v>100</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="17">
         <v>0</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="17">
         <v>10</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="11" t="s">
+      <c r="H21" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="17" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2059,183 +2078,183 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="2" width="80.8545454545455" style="7" customWidth="1"/>
-    <col min="3" max="3" width="19.2818181818182" style="7" customWidth="1"/>
-    <col min="4" max="16384" width="9.13636363636364" style="7"/>
+    <col min="1" max="2" width="80.8545454545455" style="13" customWidth="1"/>
+    <col min="3" max="3" width="19.2818181818182" style="13" customWidth="1"/>
+    <col min="4" max="16384" width="9.13636363636364" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" ht="15.5" spans="1:3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" ht="15.5" spans="1:3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" ht="15.5" spans="1:3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="9"/>
+      <c r="B5" s="15"/>
     </row>
     <row r="6" ht="15.5" spans="1:3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" ht="15.5" spans="1:3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="7" t="s">
+      <c r="B7" s="16"/>
+      <c r="C7" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" ht="15.5" spans="1:3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" ht="15.5" spans="1:3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="16"/>
+      <c r="C9" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" ht="15.5" spans="1:3">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="16"/>
+      <c r="C10" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" ht="15.5" spans="1:3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="15"/>
+      <c r="C11" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" ht="15.5" spans="1:3">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" ht="15.5" spans="1:3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" ht="15.5" spans="1:3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="14"/>
+      <c r="C14" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" ht="15.5" spans="1:3">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" ht="15.5" spans="1:3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" ht="15.5" spans="1:3">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="7" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" ht="15.5" spans="1:3">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="7" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="19" ht="15.5" spans="1:3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="14"/>
+      <c r="C19" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20" ht="15.5" spans="1:3">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B20" s="9"/>
+      <c r="B20" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2249,52 +2268,52 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="22.4272727272727" style="5" customWidth="1"/>
-    <col min="2" max="2" width="16.2818181818182" style="5" customWidth="1"/>
-    <col min="3" max="3" width="9.13636363636364" style="5"/>
-    <col min="4" max="4" width="139.854545454545" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="9.13636363636364" style="5"/>
+    <col min="1" max="1" width="22.4272727272727" style="11" customWidth="1"/>
+    <col min="2" max="2" width="16.2818181818182" style="11" customWidth="1"/>
+    <col min="3" max="3" width="9.13636363636364" style="11"/>
+    <col min="4" max="4" width="139.854545454545" style="11" customWidth="1"/>
+    <col min="5" max="16384" width="9.13636363636364" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:4">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="12" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3" ht="321.75" customHeight="1" spans="1:4">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="12" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2307,174 +2326,408 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="2"/>
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="16" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.7090909090909" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7090909090909" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.13636363636364" style="1"/>
-    <col min="6" max="6" width="19.7090909090909" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.4272727272727" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.13636363636364" style="1"/>
-    <col min="10" max="10" width="20.7090909090909" style="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5727272727273" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.1363636363636" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.8545454545455" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7090909090909" style="1" customWidth="1"/>
-    <col min="15" max="15" width="18.5727272727273" style="1" customWidth="1"/>
-    <col min="16" max="16" width="23.1363636363636" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.13636363636364" style="1"/>
+    <col min="1" max="1" width="16" style="7" customWidth="1"/>
+    <col min="2" max="2" width="18" style="7" customWidth="1"/>
+    <col min="3" max="3" width="29.7090909090909" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.7090909090909" style="7" customWidth="1"/>
+    <col min="5" max="5" width="9.13636363636364" style="7"/>
+    <col min="6" max="6" width="19.7090909090909" style="7" customWidth="1"/>
+    <col min="7" max="7" width="25.4272727272727" style="7" customWidth="1"/>
+    <col min="8" max="8" width="12" style="7" customWidth="1"/>
+    <col min="9" max="9" width="9.13636363636364" style="7"/>
+    <col min="10" max="10" width="20.7090909090909" style="7" customWidth="1"/>
+    <col min="11" max="11" width="22.5727272727273" style="7" customWidth="1"/>
+    <col min="12" max="12" width="16.1363636363636" style="7" customWidth="1"/>
+    <col min="13" max="13" width="21.8545454545455" style="7" customWidth="1"/>
+    <col min="14" max="14" width="26.5454545454545" style="7" customWidth="1"/>
+    <col min="15" max="15" width="18.5727272727273" style="7" customWidth="1"/>
+    <col min="16" max="16" width="23.1363636363636" style="7" customWidth="1"/>
+    <col min="17" max="17" width="18.2727272727273" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="9.13636363636364" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:17">
+      <c r="A1" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="8" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="1">
-        <v>1004</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="B2" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="9">
+        <v>46004</v>
+      </c>
+      <c r="L2" s="9">
+        <v>46034</v>
+      </c>
+      <c r="M2" s="9">
+        <v>46068</v>
+      </c>
+      <c r="N2" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="K2" s="3">
+      <c r="O2" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="E3" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="9">
         <v>46004</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L3" s="9">
         <v>46034</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M3" s="9">
         <v>46068</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="1">
-        <v>1005</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="K3" s="3">
-        <v>46004</v>
-      </c>
-      <c r="L3" s="3">
-        <v>46034</v>
-      </c>
-      <c r="M3" s="3">
-        <v>46068</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>10</v>
-      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="Q4" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="advitha@gmail.com"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="5" width="8.72727272727273" style="2"/>
+    <col min="6" max="6" width="14.2727272727273" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.6363636363636" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.9090909090909" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.72727272727273" style="2"/>
+    <col min="10" max="10" width="18.4545454545455" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.8181818181818" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.4545454545455" style="2" customWidth="1"/>
+    <col min="13" max="13" width="31.2727272727273" style="2" customWidth="1"/>
+    <col min="14" max="14" width="25.9090909090909" style="2" customWidth="1"/>
+    <col min="15" max="15" width="16" style="2" customWidth="1"/>
+    <col min="16" max="16" width="24.1818181818182" style="2" customWidth="1"/>
+    <col min="17" max="17" width="18.2727272727273" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="8.72727272727273" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:17">
+      <c r="A1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:17">
+      <c r="A2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K2" s="4">
+        <v>46004</v>
+      </c>
+      <c r="L2" s="4">
+        <v>46034</v>
+      </c>
+      <c r="M2" s="4">
+        <v>46068</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:17">
+      <c r="A3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="E3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K3" s="4">
+        <v>46004</v>
+      </c>
+      <c r="L3" s="4">
+        <v>46034</v>
+      </c>
+      <c r="M3" s="4">
+        <v>46068</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:17">
+      <c r="A4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K4" s="4">
+        <v>46004</v>
+      </c>
+      <c r="L4" s="4">
+        <v>46034</v>
+      </c>
+      <c r="M4" s="4">
+        <v>46068</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="Q2" r:id="rId1" display="Admin@12"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>